--- a/Web/TestCases/Cierres.xlsx
+++ b/Web/TestCases/Cierres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29584F99-2A87-4D1E-8D7B-8650938A31D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9C50FE4-8D73-4A75-B15B-B370B2AA3120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,33 +53,9 @@
     <t>pte</t>
   </si>
   <si>
-    <t>HISSAL001</t>
-  </si>
-  <si>
-    <t>HISSAL002</t>
-  </si>
-  <si>
-    <t>HISSAL003</t>
-  </si>
-  <si>
-    <t>HISSAL004</t>
-  </si>
-  <si>
     <t>Filter: clean</t>
   </si>
   <si>
-    <t>HISSAL005</t>
-  </si>
-  <si>
-    <t>HISSAL006</t>
-  </si>
-  <si>
-    <t>HISSAL007</t>
-  </si>
-  <si>
-    <t>HISSAL008</t>
-  </si>
-  <si>
     <t>closure page home</t>
   </si>
   <si>
@@ -102,6 +78,30 @@
   </si>
   <si>
     <t>Closure: Filter by restaurant</t>
+  </si>
+  <si>
+    <t>HISCLO001</t>
+  </si>
+  <si>
+    <t>HISCLO002</t>
+  </si>
+  <si>
+    <t>HISCLO003</t>
+  </si>
+  <si>
+    <t>HISCLO004</t>
+  </si>
+  <si>
+    <t>HISCLO005</t>
+  </si>
+  <si>
+    <t>HISCLO006</t>
+  </si>
+  <si>
+    <t>HISCLO007</t>
+  </si>
+  <si>
+    <t>HISCLO008</t>
   </si>
 </sst>
 </file>
@@ -586,16 +586,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="8" t="s">
@@ -608,10 +608,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -626,10 +626,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -644,10 +644,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -662,10 +662,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -680,10 +680,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -698,10 +698,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>25</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -716,10 +716,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>18</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>

--- a/Web/TestCases/Cierres.xlsx
+++ b/Web/TestCases/Cierres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9C50FE4-8D73-4A75-B15B-B370B2AA3120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11B79476-3A2B-4A71-BDBC-D92805E4F2AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="28">
   <si>
     <t>Num</t>
   </si>
@@ -46,69 +46,77 @@
     <t>Notes</t>
   </si>
   <si>
-    <t xml:space="preserve">1. 
+    <t>Filter: clean</t>
+  </si>
+  <si>
+    <t>closure page home</t>
+  </si>
+  <si>
+    <t>1. Closure page home is correctly.</t>
+  </si>
+  <si>
+    <t>Closure between dates</t>
+  </si>
+  <si>
+    <t>Filter: Closure by waiter</t>
+  </si>
+  <si>
+    <t>HISCLO001</t>
+  </si>
+  <si>
+    <t>HISCLO002</t>
+  </si>
+  <si>
+    <t>HISCLO003</t>
+  </si>
+  <si>
+    <t>HISCLO004</t>
+  </si>
+  <si>
+    <t>HISCLO005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The users clicks "Cierres"
 </t>
   </si>
   <si>
-    <t>pte</t>
-  </si>
-  <si>
-    <t>Filter: clean</t>
-  </si>
-  <si>
-    <t>closure page home</t>
-  </si>
-  <si>
-    <t>1. Closure page home is correctly.</t>
-  </si>
-  <si>
-    <t>Closure between dates</t>
-  </si>
-  <si>
-    <t>Filter: Closure by pay method</t>
-  </si>
-  <si>
-    <t>Filter: Closure by waiter</t>
-  </si>
-  <si>
-    <t>Filter: Closure by status</t>
-  </si>
-  <si>
-    <t>Export Closure</t>
-  </si>
-  <si>
-    <t>Closure: Filter by restaurant</t>
-  </si>
-  <si>
-    <t>HISCLO001</t>
-  </si>
-  <si>
-    <t>HISCLO002</t>
-  </si>
-  <si>
-    <t>HISCLO003</t>
-  </si>
-  <si>
-    <t>HISCLO004</t>
-  </si>
-  <si>
-    <t>HISCLO005</t>
-  </si>
-  <si>
-    <t>HISCLO006</t>
-  </si>
-  <si>
-    <t>HISCLO007</t>
-  </si>
-  <si>
-    <t>HISCLO008</t>
+    <t>1. Closure are shown.</t>
+  </si>
+  <si>
+    <t>1. There is not a filter</t>
+  </si>
+  <si>
+    <t>1. The user selects "desde"
+2. The user selects "hasta"</t>
+  </si>
+  <si>
+    <t>1. The user selects "desde"
+2. The user selects "hasta"
+3. The user selects waiter.</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Limpiar fitros"</t>
+  </si>
+  <si>
+    <t>BL</t>
+  </si>
+  <si>
+    <t>No se puede seleccionar nada</t>
+  </si>
+  <si>
+    <t>Filter: Closure by type</t>
+  </si>
+  <si>
+    <t>1. The user selects "desde"
+2. The user selects "hasta"
+3. The user selects type.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -127,14 +135,6 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
@@ -175,11 +175,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -196,18 +195,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="4">
@@ -545,7 +537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -586,152 +578,124 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F2" s="3"/>
-      <c r="G2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="7"/>
+      <c r="G2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="3" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
+        <v>11</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="F3" s="3"/>
-      <c r="G3" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="6"/>
+      <c r="G3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="4" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
+        <v>26</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="F4" s="3"/>
-      <c r="G4" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="4"/>
+      <c r="G4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="5" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
+      <c r="E5" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="F5" s="3"/>
-      <c r="G5" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="4"/>
+      <c r="G5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="6" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
+      <c r="E6" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="F6" s="3"/>
-      <c r="G6" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" s="4"/>
-    </row>
-    <row r="7" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
-        <v>6</v>
-      </c>
-      <c r="B7" s="4" t="s">
+      <c r="G6" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" s="4"/>
-    </row>
-    <row r="8" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
-        <v>7</v>
-      </c>
-      <c r="B8" s="4" t="s">
+      <c r="H6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="H8" s="4"/>
-    </row>
-    <row r="9" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
-        <v>8</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="H9" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="G2:G9">
+  <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="G2:G6">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
     </cfRule>
